--- a/output/c4ai_matriz_grupo_ano.xlsx
+++ b/output/c4ai_matriz_grupo_ano.xlsx
@@ -453,19 +453,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3">
@@ -509,13 +509,13 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -653,19 +653,19 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" t="n">
         <v>103</v>
       </c>
       <c r="E10" t="n">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>413</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>

--- a/output/c4ai_matriz_grupo_ano.xlsx
+++ b/output/c4ai_matriz_grupo_ano.xlsx
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
         <v>16</v>
@@ -465,7 +465,7 @@
         <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -653,7 +653,7 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" t="n">
         <v>103</v>
@@ -665,7 +665,7 @@
         <v>59</v>
       </c>
       <c r="G10" t="n">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
